--- a/ch-1-getting-started-with-python-in-excel/ch_01_solutions.xlsx
+++ b/ch-1-getting-started-with-python-in-excel/ch_01_solutions.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28407"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29607"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wiley.sharepoint.com/teams/9781394284931MountExcelPowerTools/Shared Documents/General/Stage1_ContentDevelopment/01_originalmaterialfromAU/code_files/ch09-python-in-excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\AI-Powered-Analytics-in-Excel\ch-1-getting-started-with-python-in-excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{7896E653-199D-4B50-B0F3-9D1FCD47D50C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50351979-77E3-4D06-B864-D7A5B65043A6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4680B661-5EE3-4EC5-A738-9AA62D1B0908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="18915" windowHeight="12676" activeTab="1" xr2:uid="{2E41FF59-E030-4D3D-BD6E-1467FE591C9D}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{2E41FF59-E030-4D3D-BD6E-1467FE591C9D}"/>
   </bookViews>
   <sheets>
     <sheet name="hello-world" sheetId="1" r:id="rId1"/>
-    <sheet name="nyc_pop" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029" calcMode="autoNoTable"/>
   <extLst>
@@ -51,7 +50,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="3">
+  <futureMetadata name="XLRICHVALUE" count="2">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -66,28 +65,18 @@
         </ext>
       </extLst>
     </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="2"/>
-        </ext>
-      </extLst>
-    </bk>
   </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="3">
+  <valueMetadata count="2">
     <bk>
       <rc t="2" v="0"/>
     </bk>
     <bk>
       <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
     </bk>
   </valueMetadata>
 </metadata>
@@ -117,46 +106,8 @@
     <pythonScript>
       <code>my_object.upper()</code>
     </pythonScript>
-    <pythonScript>
-      <code>nyc_df= xl(%P2%, headers=True) 
-nyc_df['density'] = nyc_df['population'] / nyc_df['land_area']
-nyc_df</code>
-    </pythonScript>
-    <pythonScript>
-      <code>nyc = xl(%P2%, headers=True)
-sns.barplot(x='borough', y='population', data=nyc)</code>
-    </pythonScript>
   </pythonScripts>
 </python>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t>Brooklyn</t>
-  </si>
-  <si>
-    <t>Queens</t>
-  </si>
-  <si>
-    <t>Manhattan</t>
-  </si>
-  <si>
-    <t>The Bronx</t>
-  </si>
-  <si>
-    <t>Staten Island</t>
-  </si>
-  <si>
-    <t>borough</t>
-  </si>
-  <si>
-    <t>population</t>
-  </si>
-  <si>
-    <t>land_area</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -190,18 +141,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <numFmt numFmtId="3" formatCode="#,##0"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -214,60 +160,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>160220</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>38870</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1" descr="Image generated by Python">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D8E7484-551B-A191-3CDA-32164DAD850E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-          <a:extLst>
-            <a:ext uri="{53484399-7A02-498B-ADA4-41CD10E50FAC}">
-              <aif:imageFormula xmlns:aif="http://schemas.microsoft.com/office/drawing/2022/imageformula" formula="nyc_pop!A8"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="2366963"/>
-          <a:ext cx="5184658" cy="4096520"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
 <rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
   <global>
@@ -309,7 +201,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="3">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
   <rv s="0">
     <fb t="s">Hello, world!</fb>
     <v>&lt;class 'str'&gt;</v>
@@ -317,7 +209,6 @@
     <v>Hello, world!</v>
     <v>Hello, world!</v>
     <v>0</v>
-    <v>1</v>
   </rv>
   <rv s="0">
     <fb t="s">HELLO, WORLD!</fb>
@@ -326,43 +217,26 @@
     <v>HELLO, WORLD!</v>
     <v>HELLO, WORLD!</v>
     <v>0</v>
-    <v>1</v>
-  </rv>
-  <rv s="1">
-    <v>0</v>
-    <v>9</v>
-    <v>Image generated by Python</v>
   </rv>
 </rvData>
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="2">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
   <s t="_python">
     <k n="Python_type" t="s"/>
     <k n="Python_typeName" t="s"/>
     <k n="Python_str" t="s"/>
     <k n="basicValue" t="s"/>
     <k n="_Provider" t="spb"/>
-    <k n="provider" t="spb"/>
-  </s>
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-    <k n="Text" t="s"/>
   </s>
 </rvStructures>
 </file>
 
 <file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
 <supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
-  <spbData count="2">
+  <spbData count="1">
     <spb s="0">
-      <v>https://www.anaconda.com/excel</v>
-      <v>https://res.cdn.office.net/officepysvc/prod-preview/anacondalogo.png</v>
-      <v>Python provided by Anaconda</v>
-    </spb>
-    <spb s="1">
       <v>https://www.anaconda.com/excel</v>
       <v>https://res.cdn.office.net/officepysvc/prod-preview/anacondalogo.png</v>
       <v>Python provided by Anaconda</v>
@@ -372,36 +246,13 @@
 </file>
 
 <file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="2">
+<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="1">
   <s>
     <k n="link" t="s"/>
     <k n="logo" t="s"/>
     <k n="name" t="s"/>
   </s>
-  <s>
-    <k n="url" t="s"/>
-    <k n="logoUrl" t="s"/>
-    <k n="description" t="s"/>
-  </s>
 </spbStructures>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-</richValueRels>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{456FF165-CB56-407D-8222-C9F0935D7D60}" name="nyc_pop" displayName="nyc_pop" ref="A1:C6" totalsRowShown="0">
-  <autoFilter ref="A1:C6" xr:uid="{456FF165-CB56-407D-8222-C9F0935D7D60}"/>
-  <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{26945669-7A59-44A7-9525-9771AA042A42}" name="borough"/>
-    <tableColumn id="2" xr3:uid="{FE6E5257-1713-4391-A556-ABA4C561800A}" name="population" dataDxfId="0"/>
-    <tableColumn id="3" xr3:uid="{AF7C1BFD-6695-479C-BA7C-EDD9506AC8E9}" name="land_area"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -722,20 +573,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E93D8D4-524A-4AAD-8291-1FDE7ECFD20A}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultRowHeight="26.65" x14ac:dyDescent="0.85"/>
+  <sheetFormatPr defaultRowHeight="26.35" x14ac:dyDescent="0.9"/>
   <cols>
-    <col min="1" max="1" width="15.109375" customWidth="1"/>
-    <col min="2" max="2" width="12.73828125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.9609375" customWidth="1"/>
+    <col min="1" max="1" width="15.09765625" customWidth="1"/>
+    <col min="2" max="2" width="12.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.96484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.85">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.9">
       <c r="B2" t="str" cm="1" vm="1">
         <f t="array" ref="B2">_xlfn._xlws.PY(0,1)</f>
         <v>Hello, world!</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.85">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.9">
       <c r="C3" t="str" cm="1" vm="2">
         <f t="array" ref="C3">_xlfn._xlws.PY(1,1)</f>
         <v>HELLO, WORLD!</v>
@@ -746,175 +597,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0079F4FB-E19A-40B4-8138-462AEEFA02CD}">
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="26.65" x14ac:dyDescent="0.85"/>
-  <cols>
-    <col min="1" max="1" width="10.92578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.18359375" customWidth="1"/>
-    <col min="3" max="3" width="9.3671875" customWidth="1"/>
-    <col min="5" max="5" width="10.92578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.58984375" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.85">
-      <c r="A1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" t="str" cm="1">
-        <f t="array" ref="E1:H6">_xlfn._xlws.PY(2,0,nyc_pop[#All])</f>
-        <v>borough</v>
-      </c>
-      <c r="F1" s="1" t="str">
-        <v>population</v>
-      </c>
-      <c r="G1" t="str">
-        <v>land_area</v>
-      </c>
-      <c r="H1" s="1" t="str">
-        <v>density</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.85">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1">
-        <v>2736074</v>
-      </c>
-      <c r="C2">
-        <v>69.5</v>
-      </c>
-      <c r="E2" t="str">
-        <v>Brooklyn</v>
-      </c>
-      <c r="F2" s="1">
-        <v>2736074</v>
-      </c>
-      <c r="G2">
-        <v>69.5</v>
-      </c>
-      <c r="H2" s="1">
-        <v>39367.971223021581</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.85">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1">
-        <v>2405464</v>
-      </c>
-      <c r="C3">
-        <v>108.7</v>
-      </c>
-      <c r="E3" t="str">
-        <v>Queens</v>
-      </c>
-      <c r="F3" s="1">
-        <v>2405464</v>
-      </c>
-      <c r="G3">
-        <v>108.7</v>
-      </c>
-      <c r="H3" s="1">
-        <v>22129.383624655013</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.85">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1694251</v>
-      </c>
-      <c r="C4">
-        <v>22.83</v>
-      </c>
-      <c r="E4" t="str">
-        <v>Manhattan</v>
-      </c>
-      <c r="F4" s="1">
-        <v>1694251</v>
-      </c>
-      <c r="G4">
-        <v>22.83</v>
-      </c>
-      <c r="H4" s="1">
-        <v>74211.607533946561</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.85">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1">
-        <v>1472654</v>
-      </c>
-      <c r="C5">
-        <v>42.1</v>
-      </c>
-      <c r="E5" t="str">
-        <v>The Bronx</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1472654</v>
-      </c>
-      <c r="G5">
-        <v>42.1</v>
-      </c>
-      <c r="H5" s="1">
-        <v>34979.904988123511</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.85">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1">
-        <v>495747</v>
-      </c>
-      <c r="C6">
-        <v>58.37</v>
-      </c>
-      <c r="E6" t="str">
-        <v>Staten Island</v>
-      </c>
-      <c r="F6" s="1">
-        <v>495747</v>
-      </c>
-      <c r="G6">
-        <v>58.37</v>
-      </c>
-      <c r="H6" s="1">
-        <v>8493.1814288161731</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.85">
-      <c r="A8" t="e" cm="1" vm="3">
-        <f t="array" ref="A8">_xlfn._xlws.PY(3,0,nyc_pop[#All])</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
-  <tableParts count="1">
-    <tablePart r:id="rId3"/>
-  </tableParts>
-</worksheet>
-</file>
-
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BBCD8F757B0C22459E37E1A3FC746090" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="796fdd032219895eba2645246eba4105">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="3d1092ee-e153-45fa-8899-22e30fa0d204" xmlns:ns3="8da6c5d4-83a2-44cb-9fdf-dd797777f83e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="55cc8a502289f914dda1d1ccbb2981a2" ns2:_="" ns3:_="">
     <xsd:import namespace="3d1092ee-e153-45fa-8899-22e30fa0d204"/>
@@ -1109,15 +801,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1130,6 +813,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6ED2E53-0F17-4E5E-A34D-76888CD516FF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{346824FF-5EEF-4ED8-9F91-F890065EEDDE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1148,14 +839,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A6ED2E53-0F17-4E5E-A34D-76888CD516FF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{523D8383-6971-49CC-BBC2-E6DD76091005}">
   <ds:schemaRefs>
